--- a/experiments/20250716_SOO/iteration_0/raw_data/raw_absorbance_i0.xlsx
+++ b/experiments/20250716_SOO/iteration_0/raw_data/raw_absorbance_i0.xlsx
@@ -5,19 +5,19 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Surfactant\0711\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Surfactant\0716\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1B1DEAD3-7426-42B2-9B9A-A6284C010418}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B6A9BC1E-DE8A-4189-B418-AEDE51173B39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="384" yWindow="384" windowWidth="9528" windowHeight="10356"/>
+    <workbookView xWindow="1500" yWindow="1500" windowWidth="9528" windowHeight="10356"/>
   </bookViews>
   <sheets>
-    <sheet name="Plate 2 - Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Plate 3 - Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="MethodPointer1">1830548720</definedName>
-    <definedName name="MethodPointer2">396</definedName>
+    <definedName name="MethodPointer1">-555416336</definedName>
+    <definedName name="MethodPointer2">296</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +46,7 @@
     <t>Experiment File Path:</t>
   </si>
   <si>
-    <t>D:\Surfactant\0711\ot-0.xpt</t>
+    <t>D:\Surfactant\0716\ot-0.xpt</t>
   </si>
   <si>
     <t>Protocol File Path:</t>
@@ -55,7 +55,7 @@
     <t>Plate Number</t>
   </si>
   <si>
-    <t>Plate 2</t>
+    <t>Plate 3</t>
   </si>
   <si>
     <t>Date</t>
@@ -97,7 +97,7 @@
     <t>Absorbance Endpoint</t>
   </si>
   <si>
-    <t>E1..F12</t>
+    <t>A1..B12</t>
   </si>
   <si>
     <t>Wavelengths:  600</t>
@@ -172,7 +172,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -187,7 +187,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FFE8F3FF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -199,55 +199,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF247CBD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF60A0D1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD8E9F9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF428EC7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3385C2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE8F3FF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7EB2DB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF247CBD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8DBCE0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBAD7EF"/>
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -279,7 +243,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="19" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -298,11 +262,11 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -311,24 +275,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -686,7 +632,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="1">
-        <v>45849</v>
+        <v>45854</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -694,7 +640,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="2">
-        <v>0.48841435185185184</v>
+        <v>0.49123842592592593</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -774,7 +720,7 @@
         <v>24</v>
       </c>
       <c r="B22">
-        <v>25.8</v>
+        <v>22.7</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
@@ -820,19 +766,43 @@
       <c r="B25" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="7"/>
-      <c r="H25" s="7"/>
-      <c r="I25" s="7"/>
-      <c r="J25" s="7"/>
-      <c r="K25" s="7"/>
-      <c r="L25" s="7"/>
-      <c r="M25" s="7"/>
-      <c r="N25" s="7"/>
-      <c r="O25" s="8">
+      <c r="C25" s="7">
+        <v>4.3999999999999997E-2</v>
+      </c>
+      <c r="D25" s="8">
+        <v>1.4379999999999999</v>
+      </c>
+      <c r="E25" s="8">
+        <v>1.4790000000000001</v>
+      </c>
+      <c r="F25" s="7">
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="G25" s="7">
+        <v>0.04</v>
+      </c>
+      <c r="H25" s="7">
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="I25" s="7">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="J25" s="7">
+        <v>6.9000000000000006E-2</v>
+      </c>
+      <c r="K25" s="7">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="L25" s="7">
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="M25" s="7">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="N25" s="7">
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="O25" s="9">
         <v>600</v>
       </c>
     </row>
@@ -840,19 +810,43 @@
       <c r="B26" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
-      <c r="G26" s="7"/>
-      <c r="H26" s="7"/>
-      <c r="I26" s="7"/>
-      <c r="J26" s="7"/>
-      <c r="K26" s="7"/>
-      <c r="L26" s="7"/>
-      <c r="M26" s="7"/>
-      <c r="N26" s="7"/>
-      <c r="O26" s="8">
+      <c r="C26" s="10">
+        <v>1.891</v>
+      </c>
+      <c r="D26" s="11">
+        <v>1.339</v>
+      </c>
+      <c r="E26" s="11">
+        <v>1.2809999999999999</v>
+      </c>
+      <c r="F26" s="7">
+        <v>0.104</v>
+      </c>
+      <c r="G26" s="7">
+        <v>0.04</v>
+      </c>
+      <c r="H26" s="7">
+        <v>3.9E-2</v>
+      </c>
+      <c r="I26" s="7">
+        <v>3.9E-2</v>
+      </c>
+      <c r="J26" s="7">
+        <v>0.04</v>
+      </c>
+      <c r="K26" s="7">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="L26" s="7">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="M26" s="7">
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="N26" s="7">
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="O26" s="9">
         <v>600</v>
       </c>
     </row>
@@ -860,19 +854,19 @@
       <c r="B27" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="7"/>
-      <c r="G27" s="7"/>
-      <c r="H27" s="7"/>
-      <c r="I27" s="7"/>
-      <c r="J27" s="7"/>
-      <c r="K27" s="7"/>
-      <c r="L27" s="7"/>
-      <c r="M27" s="7"/>
-      <c r="N27" s="7"/>
-      <c r="O27" s="8">
+      <c r="C27" s="12"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="12"/>
+      <c r="G27" s="12"/>
+      <c r="H27" s="12"/>
+      <c r="I27" s="12"/>
+      <c r="J27" s="12"/>
+      <c r="K27" s="12"/>
+      <c r="L27" s="12"/>
+      <c r="M27" s="12"/>
+      <c r="N27" s="12"/>
+      <c r="O27" s="9">
         <v>600</v>
       </c>
     </row>
@@ -880,19 +874,19 @@
       <c r="B28" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
-      <c r="G28" s="7"/>
-      <c r="H28" s="7"/>
-      <c r="I28" s="7"/>
-      <c r="J28" s="7"/>
-      <c r="K28" s="7"/>
-      <c r="L28" s="7"/>
-      <c r="M28" s="7"/>
-      <c r="N28" s="7"/>
-      <c r="O28" s="8">
+      <c r="C28" s="12"/>
+      <c r="D28" s="12"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="12"/>
+      <c r="G28" s="12"/>
+      <c r="H28" s="12"/>
+      <c r="I28" s="12"/>
+      <c r="J28" s="12"/>
+      <c r="K28" s="12"/>
+      <c r="L28" s="12"/>
+      <c r="M28" s="12"/>
+      <c r="N28" s="12"/>
+      <c r="O28" s="9">
         <v>600</v>
       </c>
     </row>
@@ -900,43 +894,19 @@
       <c r="B29" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C29" s="9">
-        <v>1.9470000000000001</v>
-      </c>
-      <c r="D29" s="9">
-        <v>1.982</v>
-      </c>
-      <c r="E29" s="10">
-        <v>1.66</v>
-      </c>
-      <c r="F29" s="11">
-        <v>0.39700000000000002</v>
-      </c>
-      <c r="G29" s="12">
-        <v>2.0779999999999998</v>
-      </c>
-      <c r="H29" s="9">
-        <v>1.9330000000000001</v>
-      </c>
-      <c r="I29" s="13">
-        <v>2.2029999999999998</v>
-      </c>
-      <c r="J29" s="9">
-        <v>1.9119999999999999</v>
-      </c>
-      <c r="K29" s="13">
-        <v>2.1880000000000002</v>
-      </c>
-      <c r="L29" s="14">
-        <v>0.13500000000000001</v>
-      </c>
-      <c r="M29" s="14">
-        <v>4.2999999999999997E-2</v>
-      </c>
-      <c r="N29" s="14">
-        <v>0.04</v>
-      </c>
-      <c r="O29" s="8">
+      <c r="C29" s="12"/>
+      <c r="D29" s="12"/>
+      <c r="E29" s="12"/>
+      <c r="F29" s="12"/>
+      <c r="G29" s="12"/>
+      <c r="H29" s="12"/>
+      <c r="I29" s="12"/>
+      <c r="J29" s="12"/>
+      <c r="K29" s="12"/>
+      <c r="L29" s="12"/>
+      <c r="M29" s="12"/>
+      <c r="N29" s="12"/>
+      <c r="O29" s="9">
         <v>600</v>
       </c>
     </row>
@@ -944,43 +914,19 @@
       <c r="B30" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C30" s="14">
-        <v>4.2999999999999997E-2</v>
-      </c>
-      <c r="D30" s="15">
-        <v>1.345</v>
-      </c>
-      <c r="E30" s="13">
-        <v>2.2589999999999999</v>
-      </c>
-      <c r="F30" s="13">
-        <v>2.1960000000000002</v>
-      </c>
-      <c r="G30" s="16">
-        <v>2.5419999999999998</v>
-      </c>
-      <c r="H30" s="16">
-        <v>2.512</v>
-      </c>
-      <c r="I30" s="15">
-        <v>1.3280000000000001</v>
-      </c>
-      <c r="J30" s="15">
-        <v>1.3089999999999999</v>
-      </c>
-      <c r="K30" s="17">
-        <v>1.1839999999999999</v>
-      </c>
-      <c r="L30" s="9">
-        <v>1.976</v>
-      </c>
-      <c r="M30" s="17">
-        <v>1.268</v>
-      </c>
-      <c r="N30" s="18">
-        <v>0.73599999999999999</v>
-      </c>
-      <c r="O30" s="8">
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="12"/>
+      <c r="G30" s="12"/>
+      <c r="H30" s="12"/>
+      <c r="I30" s="12"/>
+      <c r="J30" s="12"/>
+      <c r="K30" s="12"/>
+      <c r="L30" s="12"/>
+      <c r="M30" s="12"/>
+      <c r="N30" s="12"/>
+      <c r="O30" s="9">
         <v>600</v>
       </c>
     </row>
@@ -988,19 +934,19 @@
       <c r="B31" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="7"/>
-      <c r="G31" s="7"/>
-      <c r="H31" s="7"/>
-      <c r="I31" s="7"/>
-      <c r="J31" s="7"/>
-      <c r="K31" s="7"/>
-      <c r="L31" s="7"/>
-      <c r="M31" s="7"/>
-      <c r="N31" s="7"/>
-      <c r="O31" s="8">
+      <c r="C31" s="12"/>
+      <c r="D31" s="12"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="12"/>
+      <c r="G31" s="12"/>
+      <c r="H31" s="12"/>
+      <c r="I31" s="12"/>
+      <c r="J31" s="12"/>
+      <c r="K31" s="12"/>
+      <c r="L31" s="12"/>
+      <c r="M31" s="12"/>
+      <c r="N31" s="12"/>
+      <c r="O31" s="9">
         <v>600</v>
       </c>
     </row>
@@ -1008,19 +954,19 @@
       <c r="B32" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C32" s="7"/>
-      <c r="D32" s="7"/>
-      <c r="E32" s="7"/>
-      <c r="F32" s="7"/>
-      <c r="G32" s="7"/>
-      <c r="H32" s="7"/>
-      <c r="I32" s="7"/>
-      <c r="J32" s="7"/>
-      <c r="K32" s="7"/>
-      <c r="L32" s="7"/>
-      <c r="M32" s="7"/>
-      <c r="N32" s="7"/>
-      <c r="O32" s="8">
+      <c r="C32" s="12"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="12"/>
+      <c r="G32" s="12"/>
+      <c r="H32" s="12"/>
+      <c r="I32" s="12"/>
+      <c r="J32" s="12"/>
+      <c r="K32" s="12"/>
+      <c r="L32" s="12"/>
+      <c r="M32" s="12"/>
+      <c r="N32" s="12"/>
+      <c r="O32" s="9">
         <v>600</v>
       </c>
     </row>
